--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N52_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N52_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>62.63479107190349</v>
+        <v>10.17815354918432</v>
       </c>
       <c r="D2" t="n">
-        <v>61.94608315996122</v>
+        <v>10.0662385134937</v>
       </c>
       <c r="E2" t="n">
-        <v>11.12546769549932</v>
+        <v>1.807888500518639</v>
       </c>
       <c r="F2" t="n">
-        <v>11.15993812557143</v>
+        <v>1.813489945405357</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>39.74103737392313</v>
+        <v>6.45791857326251</v>
       </c>
       <c r="D3" t="n">
-        <v>40.82060307984767</v>
+        <v>6.633348000475247</v>
       </c>
       <c r="E3" t="n">
-        <v>11.12546769549932</v>
+        <v>1.807888500518639</v>
       </c>
       <c r="F3" t="n">
-        <v>11.15993812557143</v>
+        <v>1.813489945405357</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>63.99022544817077</v>
+        <v>10.39841163532775</v>
       </c>
       <c r="D4" t="n">
-        <v>66.407808298012</v>
+        <v>10.79126884842695</v>
       </c>
       <c r="E4" t="n">
-        <v>11.12546769549932</v>
+        <v>1.807888500518639</v>
       </c>
       <c r="F4" t="n">
-        <v>11.15993812557143</v>
+        <v>1.813489945405357</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
